--- a/data/trans_camb/IP1003-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 11,19</t>
+          <t>-1,6; 11,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 13,55</t>
+          <t>-0,59; 13,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 9,22</t>
+          <t>-2,12; 9,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 9,03</t>
+          <t>-6,06; 10,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 9,0</t>
+          <t>-6,42; 8,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 7,1</t>
+          <t>-7,04; 6,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 7,84</t>
+          <t>-2,14; 8,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 8,91</t>
+          <t>-1,52; 8,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 6,3</t>
+          <t>-3,23; 5,96</t>
         </is>
       </c>
     </row>
@@ -788,49 +788,49 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,82; —</t>
+          <t>-59,29; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,05; —</t>
+          <t>-59,96; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,75; 431,16</t>
+          <t>-69,08; 374,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,6; 371,86</t>
+          <t>-70,13; 323,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,97; 388,63</t>
+          <t>-73,33; 250,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,66; 377,93</t>
+          <t>-36,12; 376,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,09; 435,37</t>
+          <t>-35,63; 374,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,47; 339,67</t>
+          <t>-49,33; 263,86</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 8,63</t>
+          <t>-1,52; 8,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 6,34</t>
+          <t>-2,76; 5,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 7,85</t>
+          <t>-2,51; 8,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 6,62</t>
+          <t>-3,14; 7,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 4,99</t>
+          <t>-4,36; 5,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 5,92</t>
+          <t>-3,71; 6,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 6,41</t>
+          <t>-1,02; 5,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 4,15</t>
+          <t>-2,3; 4,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,3</t>
+          <t>-1,69; 5,31</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 540,52</t>
+          <t>-35,51; 525,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,1; 386,83</t>
+          <t>-58,54; 337,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,68; 468,92</t>
+          <t>-51,98; 403,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 259,92</t>
+          <t>-50,76; 275,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,68; 190,29</t>
+          <t>-68,2; 213,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,84; 223,06</t>
+          <t>-60,67; 228,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 248,35</t>
+          <t>-20,04; 207,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 169,78</t>
+          <t>-45,12; 158,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 194,64</t>
+          <t>-33,82; 183,16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 0,13</t>
+          <t>-11,93; -0,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 0,13</t>
+          <t>-12,74; -0,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,82; -1,24</t>
+          <t>-13,46; -1,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 4,73</t>
+          <t>-6,14; 4,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 6,74</t>
+          <t>-4,79; 6,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 7,74</t>
+          <t>-3,75; 8,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 0,86</t>
+          <t>-7,08; 0,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 1,56</t>
+          <t>-6,14; 1,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 2,12</t>
+          <t>-6,53; 1,63</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 101,59</t>
+          <t>-100,0; 94,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,33</t>
+          <t>-100,0; 96,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 86,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 423,1</t>
+          <t>-100,0; 329,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 360,59</t>
+          <t>-78,69; 337,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,4; 443,15</t>
+          <t>-65,08; 540,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-87,19; 70,36</t>
+          <t>-85,91; 23,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,06; 54,23</t>
+          <t>-77,2; 54,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-79,65; 67,07</t>
+          <t>-78,61; 58,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 0,47</t>
+          <t>-13,03; 1,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 2,94</t>
+          <t>-11,84; 2,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 1,52</t>
+          <t>-12,7; 1,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 3,12</t>
+          <t>-12,24; 2,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 4,0</t>
+          <t>-11,0; 4,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 4,31</t>
+          <t>-13,52; 4,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 0,05</t>
+          <t>-10,82; 0,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 0,98</t>
+          <t>-9,32; 1,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 0,29</t>
+          <t>-10,78; 0,44</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-87,81; 19,49</t>
+          <t>-84,25; 33,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-78,54; 48,01</t>
+          <t>-76,36; 41,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-88,36; 40,6</t>
+          <t>-87,46; 40,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-75,44; 53,46</t>
+          <t>-74,46; 48,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,14; 57,21</t>
+          <t>-71,15; 70,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,69; 54,65</t>
+          <t>-87,07; 88,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 6,6</t>
+          <t>-73,08; 2,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,11; 14,29</t>
+          <t>-64,98; 15,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-78,47; 11,05</t>
+          <t>-78,68; 7,9</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 5,05</t>
+          <t>-16,47; 4,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,45; -3,55</t>
+          <t>-23,44; -3,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 1,17</t>
+          <t>-18,81; 1,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 8,12</t>
+          <t>-8,03; 7,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 1,75</t>
+          <t>-11,64; 1,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 21,34</t>
+          <t>-4,54; 20,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 3,88</t>
+          <t>-9,27; 4,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,42; -2,23</t>
+          <t>-13,19; -1,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 8,26</t>
+          <t>-7,84; 8,6</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-86,19; 112,39</t>
+          <t>-88,61; 111,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 16,75</t>
+          <t>-100,0; 115,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-91,95; 53,51</t>
+          <t>-92,28; 40,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-90,71; —</t>
+          <t>-87,78; 827,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1677,24 +1677,24 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-76,22; 86,85</t>
+          <t>-72,5; 86,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,82</t>
+          <t>-100,0; 4,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 168,43</t>
+          <t>-68,87; 200,09</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 7,16</t>
+          <t>-5,92; 7,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 11,13</t>
+          <t>-4,24; 11,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,26; 19,89</t>
+          <t>0,72; 20,21</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 8,42</t>
+          <t>-10,41; 8,41</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 10,04</t>
+          <t>-10,48; 9,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 17,07</t>
+          <t>-5,15; 16,38</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 5,98</t>
+          <t>-5,78; 6,39</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 7,55</t>
+          <t>-4,62; 7,76</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 14,62</t>
+          <t>0,27; 16,05</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-83,25; 392,81</t>
+          <t>-76,53; 485,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-69,29; 589,13</t>
+          <t>-65,88; 791,44</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 1039,82</t>
+          <t>-11,19; 1272,9</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 116,79</t>
+          <t>-63,45; 100,46</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 131,8</t>
+          <t>-63,43; 118,25</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 194,75</t>
+          <t>-36,16; 194,36</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-53,37; 97,45</t>
+          <t>-49,98; 113,07</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 140,06</t>
+          <t>-42,31; 123,88</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 237,21</t>
+          <t>-0,65; 252,59</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,19</t>
+          <t>-3,39; 4,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 2,33</t>
+          <t>-4,94; 2,46</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 9,45</t>
+          <t>-0,58; 9,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 3,57</t>
+          <t>-4,91; 4,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 0,32</t>
+          <t>-7,2; 0,41</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,94; 14,99</t>
+          <t>1,88; 15,0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,73</t>
+          <t>-3,01; 3,04</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,44</t>
+          <t>-4,7; 0,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,08; 10,89</t>
+          <t>2,52; 10,85</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-66,65; 255,21</t>
+          <t>-63,87; 265,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-85,99; 163,82</t>
+          <t>-82,66; 193,19</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 487,68</t>
+          <t>-19,16; 512,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-66,88; 113,12</t>
+          <t>-66,98; 135,81</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-89,88; 24,33</t>
+          <t>-88,05; 39,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,91; 428,33</t>
+          <t>19,23; 437,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-48,89; 87,4</t>
+          <t>-50,84; 103,72</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,5; 29,89</t>
+          <t>-74,75; 27,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>30,99; 333,31</t>
+          <t>34,34; 328,48</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,53</t>
+          <t>-6,71; 0,24</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 2,18</t>
+          <t>-5,6; 2,26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,69; -0,88</t>
+          <t>-7,86; -0,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 2,93</t>
+          <t>-6,05; 2,33</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 1,38</t>
+          <t>-6,85; 0,98</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,59</t>
+          <t>-6,75; 1,86</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,33</t>
+          <t>-5,09; 0,46</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 0,81</t>
+          <t>-4,88; 0,69</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,19; -0,39</t>
+          <t>-5,99; -0,67</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-81,24; 23,49</t>
+          <t>-82,65; 22,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 61,89</t>
+          <t>-68,98; 62,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-94,02; 3,13</t>
+          <t>-100,0; -7,4</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-62,34; 67,78</t>
+          <t>-62,37; 47,88</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-73,11; 33,61</t>
+          <t>-71,35; 26,7</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-75,96; 34,89</t>
+          <t>-72,07; 52,45</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-62,42; 11,42</t>
+          <t>-63,44; 10,81</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-63,55; 19,94</t>
+          <t>-60,47; 18,74</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-75,81; -4,25</t>
+          <t>-77,35; -8,73</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,77</t>
+          <t>-3,34; 0,53</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,41</t>
+          <t>-3,31; 0,79</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,78</t>
+          <t>-2,49; 1,63</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,33</t>
+          <t>-3,09; 1,13</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,33</t>
+          <t>-3,72; 0,32</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,77</t>
+          <t>-0,99; 3,85</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,47</t>
+          <t>-2,52; 0,44</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,02; -0,09</t>
+          <t>-3,1; -0,21</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,97</t>
+          <t>-1,23; 2,12</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 16,19</t>
+          <t>-47,17; 11,26</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 9,86</t>
+          <t>-47,9; 16,58</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 35,91</t>
+          <t>-36,19; 32,58</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 22,87</t>
+          <t>-38,44; 19,19</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 4,8</t>
+          <t>-46,52; 5,85</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 65,54</t>
+          <t>-13,36; 66,37</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 8,63</t>
+          <t>-34,92; 7,84</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-41,67; -1,35</t>
+          <t>-43,33; -3,28</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 36,45</t>
+          <t>-16,5; 36,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1003-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 11,27</t>
+          <t>-1,36; 12,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 13,48</t>
+          <t>-0,4; 13,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 9,73</t>
+          <t>-1,58; 9,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 10,6</t>
+          <t>-6,59; 10,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 8,73</t>
+          <t>-6,94; 8,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 6,01</t>
+          <t>-7,27; 6,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 8,45</t>
+          <t>-2,19; 7,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 8,41</t>
+          <t>-1,55; 9,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 5,96</t>
+          <t>-2,92; 5,81</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,29; —</t>
+          <t>-65,03; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,96; —</t>
+          <t>-69,96; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,08; 374,66</t>
+          <t>-66,71; 388,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,13; 323,23</t>
+          <t>-73,79; 322,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,33; 250,08</t>
+          <t>-75,11; 334,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 376,36</t>
+          <t>-43,73; 398,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 374,09</t>
+          <t>-28,96; 447,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,33; 263,86</t>
+          <t>-47,26; 253,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 8,91</t>
+          <t>-1,25; 8,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 5,97</t>
+          <t>-3,21; 5,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 8,48</t>
+          <t>-3,12; 8,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 7,36</t>
+          <t>-2,73; 7,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 5,26</t>
+          <t>-4,3; 5,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 6,7</t>
+          <t>-4,19; 5,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 5,84</t>
+          <t>-1,5; 6,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,29</t>
+          <t>-2,56; 4,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 5,31</t>
+          <t>-2,15; 5,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 525,78</t>
+          <t>-34,78; 508,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,54; 337,77</t>
+          <t>-64,88; 302,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 403,44</t>
+          <t>-61,02; 401,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 275,96</t>
+          <t>-42,94; 329,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,2; 213,11</t>
+          <t>-69,71; 259,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,67; 228,23</t>
+          <t>-63,3; 242,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 207,48</t>
+          <t>-28,17; 221,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 158,57</t>
+          <t>-47,28; 168,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 183,16</t>
+          <t>-41,74; 190,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -0,02</t>
+          <t>-11,72; 0,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,74; -0,01</t>
+          <t>-11,99; -0,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -1,48</t>
+          <t>-13,0; -1,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 4,46</t>
+          <t>-6,23; 4,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 6,5</t>
+          <t>-4,31; 7,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 8,34</t>
+          <t>-4,1; 8,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 0,41</t>
+          <t>-7,15; 0,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 1,68</t>
+          <t>-6,4; 2,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 1,63</t>
+          <t>-6,72; 2,06</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 94,86</t>
+          <t>-100,0; 102,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,08</t>
+          <t>-100,0; 76,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 84,98</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 314,4</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 329,16</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-78,69; 337,93</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 540,64</t>
+          <t>-67,93; 517,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,91; 23,49</t>
+          <t>-90,57; 33,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-77,2; 54,5</t>
+          <t>-78,01; 77,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,61; 58,2</t>
+          <t>-79,69; 83,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 1,28</t>
+          <t>-13,56; 1,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 2,11</t>
+          <t>-11,85; 2,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 1,85</t>
+          <t>-13,93; 1,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 2,56</t>
+          <t>-11,56; 3,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 4,85</t>
+          <t>-11,51; 3,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 4,76</t>
+          <t>-13,34; 5,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 0,16</t>
+          <t>-10,01; 0,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 1,28</t>
+          <t>-9,66; 1,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 0,44</t>
+          <t>-11,11; -0,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,25; 33,98</t>
+          <t>-86,75; 36,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,36; 41,01</t>
+          <t>-76,78; 39,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-87,46; 40,25</t>
+          <t>-90,01; 44,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,46; 48,76</t>
+          <t>-72,07; 61,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,15; 70,64</t>
+          <t>-72,09; 55,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,07; 88,31</t>
+          <t>-87,0; 78,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-73,08; 2,22</t>
+          <t>-71,05; 4,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 15,64</t>
+          <t>-67,95; 20,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-78,68; 7,9</t>
+          <t>-80,4; 4,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 4,7</t>
+          <t>-16,68; 5,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-23,44; -3,42</t>
+          <t>-22,38; -3,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 1,07</t>
+          <t>-18,41; 0,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 7,16</t>
+          <t>-8,99; 7,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 1,83</t>
+          <t>-11,49; 1,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 20,89</t>
+          <t>-4,29; 20,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 4,1</t>
+          <t>-8,96; 4,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,19; -1,85</t>
+          <t>-13,17; -1,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 8,6</t>
+          <t>-7,51; 9,06</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-88,61; 111,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,22</t>
+          <t>-100,0; 213,59</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-92,28; 40,14</t>
+          <t>-92,25; 46,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-87,78; 827,54</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-72,5; 86,28</t>
+          <t>-73,14; 117,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,12</t>
+          <t>-100,0; -2,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-68,87; 200,09</t>
+          <t>-67,09; 193,31</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 7,61</t>
+          <t>-5,77; 7,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 11,2</t>
+          <t>-4,13; 11,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,72; 20,21</t>
+          <t>1,61; 19,32</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 8,41</t>
+          <t>-11,13; 8,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 9,46</t>
+          <t>-10,81; 8,9</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 16,38</t>
+          <t>-5,6; 16,78</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 6,39</t>
+          <t>-6,02; 5,83</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 7,76</t>
+          <t>-5,2; 7,54</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,27; 16,05</t>
+          <t>0,34; 15,24</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-76,53; 485,85</t>
+          <t>-80,08; 481,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-65,88; 791,44</t>
+          <t>-66,98; 624,13</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 1272,9</t>
+          <t>5,61; 1283,36</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,45; 100,46</t>
+          <t>-64,41; 105,82</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-63,43; 118,25</t>
+          <t>-69,2; 118,82</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 194,36</t>
+          <t>-37,56; 212,49</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-49,98; 113,07</t>
+          <t>-51,04; 99,64</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 123,88</t>
+          <t>-48,59; 123,91</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 252,59</t>
+          <t>0,89; 253,23</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 4,35</t>
+          <t>-3,45; 4,65</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 2,46</t>
+          <t>-5,47; 2,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 9,9</t>
+          <t>-0,92; 9,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 4,06</t>
+          <t>-5,1; 3,52</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 0,41</t>
+          <t>-7,22; 0,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,88; 15,0</t>
+          <t>2,41; 16,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,04</t>
+          <t>-3,17; 2,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 0,57</t>
+          <t>-4,94; 0,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,52; 10,85</t>
+          <t>2,32; 10,55</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-63,87; 265,45</t>
+          <t>-62,28; 264,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-82,66; 193,19</t>
+          <t>-87,47; 139,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 512,91</t>
+          <t>-27,2; 468,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 135,81</t>
+          <t>-62,68; 118,83</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-88,05; 39,63</t>
+          <t>-87,37; 28,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,23; 437,98</t>
+          <t>28,7; 469,25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 103,72</t>
+          <t>-51,59; 77,0</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-74,75; 27,22</t>
+          <t>-76,2; 12,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>34,34; 328,48</t>
+          <t>33,8; 320,07</t>
         </is>
       </c>
     </row>
@@ -2189,32 +2189,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 0,24</t>
+          <t>-7,06; 0,11</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 2,26</t>
+          <t>-5,42; 1,91</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,86; -0,95</t>
+          <t>-7,84; -1,33</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 2,33</t>
+          <t>-5,55; 2,86</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 0,98</t>
+          <t>-6,3; 1,59</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 1,86</t>
+          <t>-6,54; 1,6</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 0,69</t>
+          <t>-4,97; 0,81</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,99; -0,67</t>
+          <t>-5,96; -0,51</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-82,65; 22,61</t>
+          <t>-83,99; 9,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-68,98; 62,23</t>
+          <t>-68,45; 52,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -7,4</t>
+          <t>-93,8; -6,81</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 47,88</t>
+          <t>-62,8; 69,11</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-71,35; 26,7</t>
+          <t>-71,7; 35,88</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-72,07; 52,45</t>
+          <t>-72,45; 41,22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-63,44; 10,81</t>
+          <t>-63,83; 15,56</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-60,47; 18,74</t>
+          <t>-61,47; 17,54</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-77,35; -8,73</t>
+          <t>-76,88; -9,0</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,53</t>
+          <t>-3,36; 0,75</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,79</t>
+          <t>-3,49; 0,59</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,63</t>
+          <t>-2,58; 1,82</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,13</t>
+          <t>-3,0; 1,21</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,32</t>
+          <t>-3,9; 0,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,85</t>
+          <t>-1,11; 3,97</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,44</t>
+          <t>-2,45; 0,45</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,1; -0,21</t>
+          <t>-3,03; -0,11</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,12</t>
+          <t>-1,24; 2,08</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 11,26</t>
+          <t>-46,6; 16,39</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-47,9; 16,58</t>
+          <t>-49,28; 11,42</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 32,58</t>
+          <t>-36,71; 34,74</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 19,19</t>
+          <t>-37,68; 21,22</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-46,52; 5,85</t>
+          <t>-47,77; 5,43</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 66,37</t>
+          <t>-13,97; 66,04</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 7,84</t>
+          <t>-35,55; 7,16</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-43,33; -3,28</t>
+          <t>-42,14; -1,23</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 36,3</t>
+          <t>-18,33; 36,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1003-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,05</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,91</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,64</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>2,56</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 12,24</t>
+          <t>-6,18; 9,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 13,4</t>
+          <t>-6,6; 9,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 9,36</t>
+          <t>-7,24; 8,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 10,31</t>
+          <t>-1,91; 11,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 8,62</t>
+          <t>-0,71; 13,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 6,87</t>
+          <t>-1,15; 12,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 7,96</t>
+          <t>-2,51; 7,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 9,14</t>
+          <t>-1,72; 8,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,81</t>
+          <t>-2,44; 7,75</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23,88%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>172,29%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>245,9%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>151,62%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-7,76%</t>
+          <t>213,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-69,75; 431,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,03; —</t>
+          <t>-71,6; 371,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,96; —</t>
+          <t>-74,29; 425,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,71; 388,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,79; 322,64</t>
+          <t>-62,82; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,11; 334,36</t>
+          <t>-68,53; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 398,08</t>
+          <t>-38,66; 377,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 447,62</t>
+          <t>-39,09; 435,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 253,71</t>
+          <t>-39,56; 417,47</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>2,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 8,87</t>
+          <t>-2,93; 6,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 5,89</t>
+          <t>-4,68; 4,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 8,12</t>
+          <t>-3,99; 6,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 7,27</t>
+          <t>-1,5; 8,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 5,7</t>
+          <t>-2,83; 6,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 5,99</t>
+          <t>-0,29; 11,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 6,02</t>
+          <t>-0,93; 6,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,32</t>
+          <t>-2,51; 4,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 5,58</t>
+          <t>-1,02; 6,46</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31,77%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>91,36%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>32,75%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>64,11%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31,77%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>119,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 508,91</t>
+          <t>-51,11; 259,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-64,88; 302,6</t>
+          <t>-70,68; 190,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,02; 401,96</t>
+          <t>-64,77; 225,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 329,18</t>
+          <t>-35,44; 540,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,71; 259,7</t>
+          <t>-60,1; 386,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 242,39</t>
+          <t>-20,63; 689,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 221,58</t>
+          <t>-19,73; 248,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 168,18</t>
+          <t>-45,0; 169,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 190,41</t>
+          <t>-21,94; 240,86</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,73</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,92</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-5,43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-5,33</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,5</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>-6,46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,25</t>
+          <t>-2,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 0,15</t>
+          <t>-6,18; 4,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,99; -0,22</t>
+          <t>-4,58; 6,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,0; -1,34</t>
+          <t>-3,66; 8,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 4,35</t>
+          <t>-11,6; 0,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 7,29</t>
+          <t>-11,97; 0,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 8,35</t>
+          <t>-12,81; -1,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 0,66</t>
+          <t>-7,02; 0,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 2,06</t>
+          <t>-6,41; 1,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 2,06</t>
+          <t>-6,45; 2,28</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-25,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44,55%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-72,28%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-70,94%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-86,52%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-25,19%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>-86,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-38,24%</t>
+          <t>-36,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,15</t>
+          <t>-100,0; 423,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 76,45</t>
+          <t>-75,8; 360,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 84,98</t>
+          <t>-69,79; 479,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 314,4</t>
+          <t>-100,0; 101,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 63,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,93; 517,91</t>
+          <t>-100,0; 93,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-90,57; 33,24</t>
+          <t>-87,19; 70,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,01; 77,47</t>
+          <t>-79,06; 54,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-79,69; 83,74</t>
+          <t>-79,22; 73,66</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-4,17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,58</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-5,98</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-4,65</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-6,13</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-4,17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,4</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,93</t>
+          <t>-5,84</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-5,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 1,22</t>
+          <t>-11,25; 3,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 2,31</t>
+          <t>-11,48; 4,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 1,68</t>
+          <t>-12,68; 5,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 3,18</t>
+          <t>-14,98; 0,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 3,72</t>
+          <t>-13,1; 2,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 5,36</t>
+          <t>-13,43; 2,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 0,25</t>
+          <t>-10,26; 0,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 1,5</t>
+          <t>-9,53; 0,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,11; -0,21</t>
+          <t>-10,51; 0,67</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-36,61%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-29,82%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-40,22%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-53,26%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-41,4%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-54,6%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-36,61%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-29,82%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-43,24%</t>
+          <t>-52,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-48,53%</t>
+          <t>-45,99%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,75; 36,66</t>
+          <t>-75,44; 53,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,78; 39,2</t>
+          <t>-73,14; 57,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-90,01; 44,21</t>
+          <t>-90,2; 63,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-72,07; 61,93</t>
+          <t>-87,81; 19,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,09; 55,04</t>
+          <t>-78,54; 48,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,0; 78,53</t>
+          <t>-87,28; 50,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 4,83</t>
+          <t>-71,43; 6,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,95; 20,02</t>
+          <t>-65,11; 14,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-80,4; 4,19</t>
+          <t>-78,11; 16,9</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,38</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,61</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,64</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-5,26</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-11,09</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-7,69</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,61</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>-7,64</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-1,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 5,76</t>
+          <t>-7,59; 8,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,38; -3,32</t>
+          <t>-11,38; 1,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 0,78</t>
+          <t>-4,84; 16,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 7,99</t>
+          <t>-16,29; 5,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 1,87</t>
+          <t>-22,45; -3,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 20,3</t>
+          <t>-19,3; 1,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 4,98</t>
+          <t>-10,24; 3,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -1,83</t>
+          <t>-13,42; -2,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 9,06</t>
+          <t>-8,45; 6,15</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-67,83%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>68,47%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-41,72%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-87,91%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-60,94%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-67,83%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>102,01%</t>
+          <t>-60,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-8,64%</t>
+          <t>-20,03%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>-90,71; —</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 213,59</t>
-        </is>
-      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-92,25; 46,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-86,19; 112,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 16,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-91,36; 65,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-73,14; 117,88</t>
+          <t>-76,22; 86,85</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,68</t>
+          <t>-100,0; -13,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-67,09; 193,31</t>
+          <t>-72,21; 131,94</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,13</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5,5</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,81</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>3,24</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>9,79</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>10,22</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,79</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 7,08</t>
+          <t>-11,57; 8,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 11,71</t>
+          <t>-10,34; 10,04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,61; 19,32</t>
+          <t>-5,32; 18,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 8,14</t>
+          <t>-6,2; 7,16</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 8,9</t>
+          <t>-3,85; 11,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 16,78</t>
+          <t>1,64; 20,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 5,83</t>
+          <t>-5,71; 5,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 7,54</t>
+          <t>-4,83; 7,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,34; 15,24</t>
+          <t>0,19; 15,04</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-9,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-8,39%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>43,71%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>66,34%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>200,38%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-9,0%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-8,39%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>209,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-80,08; 481,34</t>
+          <t>-64,43; 116,79</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 624,13</t>
+          <t>-62,83; 131,8</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5,61; 1283,36</t>
+          <t>-34,72; 202,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,41; 105,82</t>
+          <t>-83,25; 392,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-69,2; 118,82</t>
+          <t>-69,29; 589,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 212,49</t>
+          <t>-13,0; 1114,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,04; 99,64</t>
+          <t>-53,37; 97,45</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 123,91</t>
+          <t>-44,52; 140,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,89; 253,23</t>
+          <t>-3,36; 247,45</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,7</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8,53</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,37</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-1,16</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>4,13</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,99</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,35</t>
+          <t>6,83</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,65</t>
+          <t>-5,26; 3,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 2,18</t>
+          <t>-7,2; 0,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 9,74</t>
+          <t>2,28; 15,07</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 3,52</t>
+          <t>-3,49; 4,19</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,63</t>
+          <t>-4,9; 2,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,41; 16,02</t>
+          <t>-0,15; 10,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,41</t>
+          <t>-3,0; 2,73</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 0,27</t>
+          <t>-4,89; 0,44</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,32; 10,55</t>
+          <t>2,69; 11,42</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-12,41%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-56,4%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>152,14%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>9,62%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-30,49%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>108,15%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-12,41%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-56,4%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>142,44%</t>
+          <t>125,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>134,11%</t>
+          <t>144,27%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-62,28; 264,29</t>
+          <t>-66,88; 113,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-87,47; 139,82</t>
+          <t>-89,88; 24,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 468,13</t>
+          <t>25,17; 447,03</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-62,68; 118,83</t>
+          <t>-66,65; 255,21</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-87,37; 28,99</t>
+          <t>-85,99; 163,82</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,7; 469,25</t>
+          <t>-16,12; 536,4</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 77,0</t>
+          <t>-48,89; 87,4</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-76,2; 12,0</t>
+          <t>-75,5; 29,89</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33,8; 320,07</t>
+          <t>35,36; 351,99</t>
         </is>
       </c>
     </row>
@@ -2136,34 +2136,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-1,66</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-2,67</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-2,72</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-3,0</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-1,55</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-4,27</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-2,66</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>-2,32</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>-3,42</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 0,11</t>
+          <t>-5,83; 2,93</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 1,91</t>
+          <t>-6,78; 1,38</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,84; -1,33</t>
+          <t>-6,99; 1,64</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 2,86</t>
+          <t>-6,69; 0,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 1,59</t>
+          <t>-5,58; 2,18</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 1,6</t>
+          <t>-7,65; -0,72</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,46</t>
+          <t>-5,16; 0,33</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,81</t>
+          <t>-5,33; 0,81</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -0,51</t>
+          <t>-6,18; -0,49</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-23,55%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-37,83%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-38,48%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-51,3%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-26,51%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-72,95%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-23,55%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-37,83%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-37,67%</t>
+          <t>-72,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-51,84%</t>
+          <t>-52,8%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-83,99; 9,61</t>
+          <t>-62,34; 67,78</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-68,45; 52,82</t>
+          <t>-73,11; 33,61</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-93,8; -6,81</t>
+          <t>-75,83; 39,79</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 69,11</t>
+          <t>-81,24; 23,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-71,7; 35,88</t>
+          <t>-71,05; 61,89</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-72,45; 41,22</t>
+          <t>-94,82; 10,31</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-63,83; 15,56</t>
+          <t>-62,42; 11,42</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-61,47; 17,54</t>
+          <t>-63,55; 19,94</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-76,88; -9,0</t>
+          <t>-75,43; -6,2</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,73</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1,45</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-1,27</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-1,41</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,75</t>
+          <t>-2,86; 1,33</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,59</t>
+          <t>-3,59; 0,33</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,82</t>
+          <t>-0,9; 3,98</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 1,21</t>
+          <t>-3,24; 0,77</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,26</t>
+          <t>-3,52; 0,41</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,97</t>
+          <t>-2,02; 2,42</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,45</t>
+          <t>-2,37; 0,47</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,03; -0,11</t>
+          <t>-3,02; -0,09</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,08</t>
+          <t>-0,81; 2,44</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-11,71%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-25,05%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-21,26%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-23,55%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-7,61%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-11,71%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-25,05%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 16,39</t>
+          <t>-36,97; 22,87</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-49,28; 11,42</t>
+          <t>-46,7; 4,8</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 34,74</t>
+          <t>-12,58; 68,31</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 21,22</t>
+          <t>-46,57; 16,19</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 5,43</t>
+          <t>-49,62; 9,86</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 66,04</t>
+          <t>-29,43; 48,49</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 7,16</t>
+          <t>-33,41; 8,63</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-42,14; -1,23</t>
+          <t>-41,67; -1,35</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 36,45</t>
+          <t>-11,57; 41,23</t>
         </is>
       </c>
     </row>
